--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>520</v>
+        <v>606</v>
       </c>
       <c r="C2">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="D2">
-        <v>1330</v>
+        <v>1390</v>
       </c>
       <c r="E2">
-        <v>1483</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>542</v>
+        <v>643</v>
       </c>
       <c r="C3">
-        <v>1002</v>
+        <v>1097</v>
       </c>
       <c r="D3">
-        <v>1341</v>
+        <v>1406</v>
       </c>
       <c r="E3">
-        <v>1490</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="C4">
-        <v>1039</v>
+        <v>1056</v>
       </c>
       <c r="D4">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="E4">
-        <v>1537</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>663</v>
+        <v>727</v>
       </c>
       <c r="C5">
-        <v>1132</v>
+        <v>1202</v>
       </c>
       <c r="D5">
-        <v>1437</v>
+        <v>1469</v>
       </c>
       <c r="E5">
-        <v>1589</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>648</v>
+        <v>710</v>
       </c>
       <c r="C6">
-        <v>1123</v>
+        <v>1175</v>
       </c>
       <c r="D6">
-        <v>1432</v>
+        <v>1458</v>
       </c>
       <c r="E6">
-        <v>1586</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="C7">
-        <v>1177</v>
+        <v>1212</v>
       </c>
       <c r="D7">
-        <v>1472</v>
+        <v>1496</v>
       </c>
       <c r="E7">
-        <v>1595</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>286</v>
+        <v>465</v>
       </c>
       <c r="C8">
-        <v>722</v>
+        <v>914</v>
       </c>
       <c r="D8">
-        <v>1115</v>
+        <v>1280</v>
       </c>
       <c r="E8">
-        <v>1433</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>607</v>
+        <v>749</v>
       </c>
       <c r="C9">
-        <v>1065</v>
+        <v>1177</v>
       </c>
       <c r="D9">
-        <v>1396</v>
+        <v>1442</v>
       </c>
       <c r="E9">
-        <v>1547</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>683</v>
+        <v>754</v>
       </c>
       <c r="C10">
-        <v>1158</v>
+        <v>1211</v>
       </c>
       <c r="D10">
-        <v>1464</v>
+        <v>1490</v>
       </c>
       <c r="E10">
-        <v>1590</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>687</v>
+        <v>756</v>
       </c>
       <c r="C11">
-        <v>1161</v>
+        <v>1209</v>
       </c>
       <c r="D11">
-        <v>1466</v>
+        <v>1494</v>
       </c>
       <c r="E11">
-        <v>1592</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>701</v>
+        <v>821</v>
       </c>
       <c r="C12">
-        <v>1172</v>
+        <v>1235</v>
       </c>
       <c r="D12">
-        <v>1472</v>
+        <v>1487</v>
       </c>
       <c r="E12">
-        <v>1594</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>682</v>
+        <v>750</v>
       </c>
       <c r="C13">
-        <v>1156</v>
+        <v>1204</v>
       </c>
       <c r="D13">
-        <v>1462</v>
+        <v>1487</v>
       </c>
       <c r="E13">
-        <v>1588</v>
+        <v>1608</v>
       </c>
     </row>
   </sheetData>
